--- a/data/resultats_description_terrain_ogf.xlsx
+++ b/data/resultats_description_terrain_ogf.xlsx
@@ -39,13 +39,13 @@
     <t xml:space="preserve">CIR_max_se</t>
   </si>
   <si>
-    <t xml:space="preserve">nha_tgb_moy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nha_tgb_med</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nha_tgb_se</t>
+    <t xml:space="preserve">nha_tgb_240_moy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nha_tgb_240_med</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nha_tgb_240_se</t>
   </si>
   <si>
     <t xml:space="preserve">vol_vivant_moy</t>
@@ -708,13 +708,13 @@
         <v>5.15452437574964</v>
       </c>
       <c r="H2" t="n">
-        <v>10.8253100726121</v>
+        <v>10.3155981633636</v>
       </c>
       <c r="I2" t="n">
-        <v>9.09456817667973</v>
+        <v>7.07355302630646</v>
       </c>
       <c r="J2" t="n">
-        <v>0.573499420722412</v>
+        <v>0.828579318889262</v>
       </c>
       <c r="K2" t="n">
         <v>323.96283023966</v>
@@ -927,13 +927,13 @@
         <v>22.3374125627835</v>
       </c>
       <c r="I2" t="n">
-        <v>9.99139364965787</v>
+        <v>6.36619772367581</v>
       </c>
       <c r="J2" t="n">
-        <v>9.99139364965787</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>5.03990653124335</v>
+        <v>4.24413181578388</v>
       </c>
       <c r="L2" t="n">
         <v>348.800654759033</v>
@@ -1028,13 +1028,13 @@
         <v>36.4980973628916</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5050312429346</v>
+        <v>4.71570201753764</v>
       </c>
       <c r="J3" t="n">
-        <v>12.5050312429346</v>
+        <v>3.53677651315323</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4104630662549</v>
+        <v>3.11914369887254</v>
       </c>
       <c r="L3" t="n">
         <v>224.739999001777</v>
@@ -1129,13 +1129,13 @@
         <v>7.44320055943015</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5781710076159</v>
+        <v>10.6103295394597</v>
       </c>
       <c r="J4" t="n">
-        <v>12.7323954473516</v>
+        <v>10.6103295394597</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7870850533465</v>
+        <v>2.04195887193256</v>
       </c>
       <c r="L4" t="n">
         <v>255.573729614312</v>
@@ -1230,13 +1230,13 @@
         <v>9.28048623546731</v>
       </c>
       <c r="I5" t="n">
-        <v>13.3049488593262</v>
+        <v>14.2511288912351</v>
       </c>
       <c r="J5" t="n">
-        <v>10.8629564332563</v>
+        <v>10.6103295394597</v>
       </c>
       <c r="K5" t="n">
-        <v>1.25193047457203</v>
+        <v>1.82568321339913</v>
       </c>
       <c r="L5" t="n">
         <v>345.546856491314</v>
@@ -1331,13 +1331,13 @@
         <v>28.7797169694828</v>
       </c>
       <c r="I6" t="n">
-        <v>6.92309967622312</v>
+        <v>3.03152272555991</v>
       </c>
       <c r="J6" t="n">
-        <v>7.07355302630646</v>
+        <v>3.53677651315323</v>
       </c>
       <c r="K6" t="n">
-        <v>1.99059764752341</v>
+        <v>1.20274458744929</v>
       </c>
       <c r="L6" t="n">
         <v>228.986239630633</v>
@@ -1432,13 +1432,13 @@
         <v>6.12762496854222</v>
       </c>
       <c r="I7" t="n">
-        <v>9.00002957909005</v>
+        <v>9.33708999472453</v>
       </c>
       <c r="J7" t="n">
-        <v>9.03842886694714</v>
+        <v>7.07355302630646</v>
       </c>
       <c r="K7" t="n">
-        <v>0.541928827212867</v>
+        <v>0.967979758779071</v>
       </c>
       <c r="L7" t="n">
         <v>338.362040608698</v>
@@ -1588,13 +1588,13 @@
         <v>285</v>
       </c>
       <c r="G2" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="H2" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="n">
         <v>324</v>
@@ -1684,10 +1684,10 @@
         <v>108</v>
       </c>
       <c r="C2" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="E2" t="n">
         <v>57</v>
@@ -1792,10 +1792,10 @@
         <v>231.4</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>348.8</v>
@@ -1836,10 +1836,10 @@
         <v>222.7</v>
       </c>
       <c r="E3" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="G3" t="n">
         <v>224.7</v>
@@ -1880,10 +1880,10 @@
         <v>297.9</v>
       </c>
       <c r="E4" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7</v>
+        <v>10.6</v>
       </c>
       <c r="G4" t="n">
         <v>255.6</v>
@@ -1924,10 +1924,10 @@
         <v>308</v>
       </c>
       <c r="E5" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="F5" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="G5" t="n">
         <v>345.5</v>
@@ -1968,10 +1968,10 @@
         <v>239.7</v>
       </c>
       <c r="E6" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
         <v>229</v>
@@ -2012,10 +2012,10 @@
         <v>278.3</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="G7" t="n">
         <v>338.4</v>
